--- a/seol/230117/Calc_As_input_xlwings.xlsx
+++ b/seol/230117/Calc_As_input_xlwings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ESC\seol\230117\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CC92D5-4DB7-4106-A179-158D67C76CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D1C31B-EAAA-473C-B217-E97F811ABBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -399,7 +399,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -433,16 +433,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -615,14 +612,19 @@
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
+      <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>24</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="731520" cy="190500"/>
+        <xdr:to>
+          <xdr:col>25</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="1027" name="Drop Down 3" hidden="1">
@@ -631,7 +633,7 @@
                   <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE75C64F-05E6-4DEF-9041-C586BF1690D4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -662,20 +664,25 @@
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
-      </xdr:oneCellAnchor>
+      </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
+      <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>10</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="731520" cy="190500"/>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="1028" name="Drop Down 4" hidden="1">
@@ -684,7 +691,7 @@
                   <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F886CCB-87D7-477C-841D-F3877CD16680}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -715,20 +722,25 @@
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
-      </xdr:oneCellAnchor>
+      </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
+      <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>24</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="731520" cy="190500"/>
+        <xdr:to>
+          <xdr:col>25</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="1029" name="Drop Down 5" hidden="1">
@@ -737,7 +749,7 @@
                   <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86097483-B1FF-4CD6-80FD-D3D23BA33909}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -768,20 +780,25 @@
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
-      </xdr:oneCellAnchor>
+      </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
+      <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>10</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="731520" cy="190500"/>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="1030" name="Drop Down 6" hidden="1">
@@ -790,7 +807,7 @@
                   <a14:compatExt spid="_x0000_s1030"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EF5ABEA-3AB0-49C7-B9CF-555F17462569}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -821,7 +838,7 @@
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
-      </xdr:oneCellAnchor>
+      </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
@@ -1153,7 +1170,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="2.59765625" style="1" customWidth="1"/>
-    <col min="3" max="7" width="9.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9.59765625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.59765625" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.09765625" style="1" bestFit="1" customWidth="1"/>
@@ -1176,7 +1195,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1305,9 +1324,9 @@
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -1332,21 +1351,21 @@
       <c r="F10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="13" t="s">
+      <c r="M10" s="11"/>
+      <c r="N10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="13" t="s">
+      <c r="O10" s="13"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="R10" s="14"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="13" t="s">
+      <c r="R10" s="13"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="U10" s="14"/>
+      <c r="U10" s="13"/>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2"/>

--- a/seol/230117/Calc_As_input_xlwings.xlsx
+++ b/seol/230117/Calc_As_input_xlwings.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ESC\seol\230117\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA32B4C-D10D-483E-A291-DA972118145B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74145098-8B61-4796-A907-D971B62A37D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="단면1극한" sheetId="37" r:id="rId2"/>
-    <sheet name="단면1극단" sheetId="38" r:id="rId3"/>
-    <sheet name="단면2극한" sheetId="39" r:id="rId4"/>
+    <sheet name="단면1극한" sheetId="40" r:id="rId2"/>
+    <sheet name="단면1극단" sheetId="41" r:id="rId3"/>
+    <sheet name="단면2극한" sheetId="42" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -867,13 +867,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -882,10 +885,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2292,7 +2292,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB02BC7D-D081-4E59-9FE7-710ADAC5363D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CB0F52-CB03-42AE-BF16-05146933F3AD}">
   <dimension ref="A1:Z200"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -2390,80 +2390,80 @@
     <row r="4" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22" t="s">
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22" t="s">
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22" t="s">
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="23"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="18"/>
       <c r="Y4" s="15"/>
       <c r="Z4" s="15"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
-      <c r="C5" s="19">
+      <c r="C5" s="23">
         <v>1000</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17">
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20">
         <v>800</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17">
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20">
         <v>666.66700000000003</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17">
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20">
         <v>133.333</v>
       </c>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="18">
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="19">
         <v>179760000</v>
       </c>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="18">
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="19">
         <v>1071048</v>
       </c>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="21"/>
       <c r="Y5" s="15"/>
       <c r="Z5" s="15"/>
     </row>
@@ -8183,11 +8183,12 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6A32CF-F2A6-4319-9C95-57E321AE87D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B917A30-ABEF-41B2-84F2-5DDE501580C8}">
   <dimension ref="A1:Z200"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -8285,80 +8286,80 @@
     <row r="4" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22" t="s">
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22" t="s">
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22" t="s">
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="23"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="18"/>
       <c r="Y4" s="15"/>
       <c r="Z4" s="15"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
-      <c r="C5" s="19">
+      <c r="C5" s="23">
         <v>1000</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17">
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20">
         <v>800</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17">
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20">
         <v>666.66700000000003</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17">
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20">
         <v>133.333</v>
       </c>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="18">
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="19">
         <v>215712000</v>
       </c>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="18">
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="19">
         <v>1285257.5999999999</v>
       </c>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="21"/>
       <c r="Y5" s="15"/>
       <c r="Z5" s="15"/>
     </row>
@@ -14082,7 +14083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76E9AE3-082A-4A10-B1B6-5471AC220FA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3565F2-CE93-41DA-B992-E97EDD3E5A4D}">
   <dimension ref="A1:Z200"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -14180,80 +14181,80 @@
     <row r="4" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22" t="s">
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22" t="s">
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22" t="s">
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="23"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="18"/>
       <c r="Y4" s="15"/>
       <c r="Z4" s="15"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
-      <c r="C5" s="19">
+      <c r="C5" s="23">
         <v>1000</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17">
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20">
         <v>800</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17">
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20">
         <v>666.66700000000003</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17">
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20">
         <v>133.333</v>
       </c>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="18">
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="19">
         <v>215712000</v>
       </c>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="18">
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="19">
         <v>1285257.5999999999</v>
       </c>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="21"/>
       <c r="Y5" s="15"/>
       <c r="Z5" s="15"/>
     </row>

--- a/seol/230117/Calc_As_input_xlwings.xlsx
+++ b/seol/230117/Calc_As_input_xlwings.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ESC\seol\230117\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74145098-8B61-4796-A907-D971B62A37D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA39A436-BD81-4001-B870-D787771A3160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="단면1극한" sheetId="40" r:id="rId2"/>
-    <sheet name="단면1극단" sheetId="41" r:id="rId3"/>
-    <sheet name="단면2극한" sheetId="42" r:id="rId4"/>
+    <sheet name="단면1극한" sheetId="46" r:id="rId2"/>
+    <sheet name="단면1극단" sheetId="47" r:id="rId3"/>
+    <sheet name="단면2극한" sheetId="48" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="180">
   <si>
     <t>Φc</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -561,6 +561,75 @@
   </si>
   <si>
     <t xml:space="preserve">     = 1606572.0 N ≥ 1597301.2 N  → ∴ 추가 주철근 필요</t>
+  </si>
+  <si>
+    <t>fck = 35 Mpa, fy = 500 Mpa, Øc = 1.00, Øs = 1.00, Es = 200000 Mpa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ──────────── As² - fyd x d x As + Mu = 0 ,   Asreq =  652.5mm²</t>
+  </si>
+  <si>
+    <t>5) 사용철근량 : Asuse =  4645.2 mm², 철근도심 : dc =  133.3 mm [ 사용율 = 7.119 ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   = As_req x 4 / 3 =  870.0 mm²</t>
+  </si>
+  <si>
+    <t>As,use = 4645.2 mm² ≥ As,min =  870.0 mm²  ∴ O.K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  = 1.00 x 4645.2 x 500 / (0.80 x 1.00 x 0.85 x 35 x 1000.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  =   97.6 mm &lt; Cmax =  266.7 mm  ∴ O.K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    = (666.7 - 97.6) / 97.6 x 0.00330 = 0.01924 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> = 1.00 x 500 / 200000 = 0.00250  ≤ εs  ∴ 항복가정 O.K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   = 4645.2 x 1.00 x 500 x (666.7 - 0.40 x 97.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   = 1457736625.9 N.mm  ≥ Mu = 215712000.0 N.mm  ∴ O.K  [S.F = 6.758]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    = [0.85 x 1.00 x 1.548 x (0.006968 x 35.0)⅓ + 0.15 x 0.000] x 1000.0 x 666.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    =     547951 N</t>
+  </si>
+  <si>
+    <t>fn = Nu / Ac = 0.000 MPa (≤ 0.2 Φc fck = 7.000 MPa, 압축의경우+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        = (0.4 x 1.00 x 2.415 + 0.15 x 0.000] x 1000.0 x 666.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        =    644018 N</t>
+  </si>
+  <si>
+    <t>Vcd =    644018 N &lt; Vu =   1285258 N  ∴ 전단보강 필요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    = (1.00 x 500.0 x 794.4 x 600.0 / 300.0) x 2.500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    = 1986000 N ≥ Vu = 1285257 N  ∴ O.K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        = (0.516 x 1.00 x 35.0 x 1000.0 x 600.0) / ( 2.500 + 0.400 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        = 3736551 N ≤ Vsd = 1986000 N  ∴ O.K</t>
+  </si>
+  <si>
+    <t>ΔTr = (Mr - Mu) / z = (1457736625.9 - 215712000.0) / 666.7 = 1863036.9 N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     = 1606572.0 N &lt; 1863036.9 N  → ∴ 추가 주철근 필요 없음</t>
   </si>
 </sst>
 </file>
@@ -2292,7 +2361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CB0F52-CB03-42AE-BF16-05146933F3AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E5B156-2946-4C32-8DF7-9AD10D575507}">
   <dimension ref="A1:Z200"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -8183,12 +8252,11 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B917A30-ABEF-41B2-84F2-5DDE501580C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0E1A1D-3461-47DB-B10B-3DE6E7C3D93A}">
   <dimension ref="A1:Z200"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -8257,7 +8325,7 @@
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
@@ -8579,7 +8647,7 @@
         <v>64</v>
       </c>
       <c r="Q12" s="16">
-        <v>19.337499999999999</v>
+        <v>29.75</v>
       </c>
       <c r="R12" s="16"/>
       <c r="S12" s="15" t="s">
@@ -8881,7 +8949,7 @@
         <v>64</v>
       </c>
       <c r="Q21" s="16">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="R21" s="16"/>
       <c r="S21" s="15" t="s">
@@ -8917,7 +8985,7 @@
         <v>64</v>
       </c>
       <c r="Q22" s="16">
-        <v>2.2499999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="R22" s="16"/>
       <c r="S22" s="15"/>
@@ -9111,7 +9179,7 @@
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
@@ -9198,7 +9266,7 @@
     <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="15" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
@@ -9438,7 +9506,7 @@
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
       <c r="D40" s="15" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -9467,7 +9535,7 @@
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D41" s="15"/>
       <c r="E41" s="15"/>
@@ -9675,7 +9743,7 @@
       <c r="A48" s="15"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="D48" s="15"/>
       <c r="E48" s="15"/>
@@ -9705,7 +9773,7 @@
       <c r="A49" s="15"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
@@ -9823,7 +9891,7 @@
       <c r="A53" s="15"/>
       <c r="B53" s="15"/>
       <c r="C53" s="15" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="15"/>
@@ -9884,7 +9952,7 @@
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
       <c r="D55" s="15" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
@@ -10001,7 +10069,7 @@
       <c r="A59" s="15"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15" t="s">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="D59" s="15"/>
       <c r="E59" s="15"/>
@@ -10031,7 +10099,7 @@
       <c r="A60" s="15"/>
       <c r="B60" s="15"/>
       <c r="C60" s="15" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D60" s="15"/>
       <c r="E60" s="15"/>
@@ -10149,7 +10217,7 @@
       <c r="A64" s="15"/>
       <c r="B64" s="15"/>
       <c r="C64" s="15" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="D64" s="15"/>
       <c r="E64" s="15"/>
@@ -10179,7 +10247,7 @@
       <c r="A65" s="15"/>
       <c r="B65" s="15"/>
       <c r="C65" s="15" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="D65" s="15"/>
       <c r="E65" s="15"/>
@@ -10270,7 +10338,7 @@
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
       <c r="D68" s="15" t="s">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="E68" s="15"/>
       <c r="F68" s="15"/>
@@ -10329,7 +10397,7 @@
       <c r="A70" s="15"/>
       <c r="B70" s="15"/>
       <c r="C70" s="15" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="D70" s="15"/>
       <c r="E70" s="15"/>
@@ -10359,7 +10427,7 @@
       <c r="A71" s="15"/>
       <c r="B71" s="15"/>
       <c r="C71" s="15" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D71" s="15"/>
       <c r="E71" s="15"/>
@@ -10389,7 +10457,7 @@
       <c r="A72" s="15"/>
       <c r="B72" s="15"/>
       <c r="C72" s="15" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D72" s="15"/>
       <c r="E72" s="15"/>
@@ -10567,7 +10635,7 @@
       <c r="A78" s="15"/>
       <c r="B78" s="15"/>
       <c r="C78" s="15" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="D78" s="15"/>
       <c r="E78" s="15"/>
@@ -10597,7 +10665,7 @@
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D79" s="15"/>
       <c r="E79" s="15"/>
@@ -10657,7 +10725,7 @@
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="15" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="D81" s="15"/>
       <c r="E81" s="15"/>
@@ -10687,7 +10755,7 @@
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
       <c r="C82" s="15" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="D82" s="15"/>
       <c r="E82" s="15"/>
@@ -11011,7 +11079,7 @@
       <c r="A93" s="15"/>
       <c r="B93" s="15"/>
       <c r="C93" s="15" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D93" s="15"/>
       <c r="E93" s="15"/>
@@ -11071,7 +11139,7 @@
       <c r="A95" s="15"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D95" s="15"/>
       <c r="E95" s="15"/>
@@ -14083,7 +14151,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3565F2-CE93-41DA-B992-E97EDD3E5A4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975DE119-BFC4-4063-83CB-BFD77E73F5EB}">
   <dimension ref="A1:Z200"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
